--- a/course-design-2/outputs/tables/ch4/29_reopen_statistics.xlsx
+++ b/course-design-2/outputs/tables/ch4/29_reopen_statistics.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_三档口径汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_三档统计范围汇总" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_三档明细指标" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_T1间隔分布（日历天）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_T2间隔取值明细（日历天）" sheetId="4" state="visible" r:id="rId4"/>

--- a/course-design-2/outputs/tables/ch4/29_reopen_statistics.xlsx
+++ b/course-design-2/outputs/tables/ch4/29_reopen_statistics.xlsx
@@ -436,7 +436,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
